--- a/Dataset/EN/xlsx/ITAMed_2020_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2020_EN.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Raynaud's phenomenon</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Livedo reticularis</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -564,12 +564,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Scleroderma</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Fibromyalgia</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Scleroderma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Inhaled administration of salbutamol</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Intravenous administration of atropine</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Inhaled administration of salbutamol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Increased BNP levels</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Hypertension</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Increased BNP levels</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Atenolol</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Furosemide</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Atenolol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Administer intravenous epinephrine</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Immediately begin cardiopulmonary resuscitation maneuvers</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Administer intravenous epinephrine</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Colchicine</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Acetaminophen</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Colchicine</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Warfarin must be started and continued in combination with subcutaneous heparin until the therapeutic INR range (between 2 and 3) is reached; heparin can then be discontinued after at least 48 hours</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Warfarin (maintaining an INR range between 2 and 3) must be started and continued in combination with subcutaneous heparin for at least 1 month</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Warfarin must be started and continued in combination with subcutaneous heparin until the therapeutic INR range (between 2 and 3) is reached; heparin can then be discontinued after at least 48 hours</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -970,14 +970,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Activated charcoal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Sodium sucralfate</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Activated charcoal</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Kayexalate</t>
@@ -990,7 +990,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cholestyramine 3</t>
+          <t>Cholestyramine</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Lhermitte's sign</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Stewart-Holmes sign</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Lhermitte's sign</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Oral anticoagulant therapy with an INR value within the therapeutic range</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Blood pressure 140/90 mmHg</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Oral anticoagulant therapy with an INR value within the therapeutic range</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Intravenous epinephrine</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Intravenous aminophylline</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Intravenous epinephrine</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Infusion of purified coagulation factors (prothrombin complex)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Vitamin K</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Infusion of purified coagulation factors (prothrombin complex)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Doppler ultrasound of the abdominal aorta</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>CT angiography of the abdominal aorta</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Doppler ultrasound of the abdominal aorta</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Finasteride</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Sildenafil</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Finasteride</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Patient with a mechanical heart valve</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Treatment of pulmonary thromboembolism</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Patient with a mechanical heart valve</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1434,14 +1434,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Endoscopic cholangioscopy with possible placement of a stent for biliary drainage</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Neoadjuvant chemotherapy followed by surgery</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Endoscopic cholangioscopy with possible placement of a stent for biliary drainage</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Neoadjuvant radiotherapy and chemotherapy followed by surgery</t>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Esophagogastroduodenoscopy on the 5th</t>
+          <t>Esophagogastroduodenoscopy</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Ewing sarcoma</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Hodgkin lymphoma</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Ewing sarcoma</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Osimertinib</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Chemotherapy</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Osimertinib</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Discontinuation of the drug and immediate hospitalization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Immediate discontinuation of the drug and prescription of topical steroid therapy</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Discontinuation of the drug and immediate hospitalization</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Systemic antibiotics</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Corticosteroids</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Systemic antibiotics</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Genital herpes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Primary syphilis</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Genital herpes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Bone marrow aspirate and peripheral venous blood smear</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>D-dimer measurement</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Bone marrow aspirate and peripheral venous blood smear</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Red cell mass measurement</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Ferritin level</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Red cell mass measurement</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>T-cell lymphoblastic leukemia</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>B-cell lymphoblastic leukemia</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>T-cell lymphoblastic leukemia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>The presence of atrophic gastritis does not reduce L-thyroxine absorption</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Taking L-thyroxine in a non-fasting state may alter its absorption</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>The presence of atrophic gastritis does not reduce L-thyroxine absorption</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Sheehan syndrome</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Pregnancy</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Sheehan syndrome</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Methylprednisolone</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>Risedronate</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Methylprednisolone</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Class II obesity</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>Class I obesity</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Class II obesity</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Schatzki ring</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Esophageal adenocarcinoma</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Schatzki ring</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Metoclopramide</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Amitriptyline</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Metoclopramide</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Mycophenolate</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Sulfasalazine</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Mycophenolate</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2357,17 +2357,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A 58-year-old man subjected to high levels of stress in the workplace, not on pharmacological treatment for arterial hypertension and with a medical history negative for significant conditions, presents to his general practitioner for a blood pressure check, reporting the finding of elevated blood pressure values (around 155/95 mmHg) during occasional measurements taken at the workplace. The physician finds levels of 138/88 mmHg (average of multiple measurements). In subjects not on antihypertensive treatment, as in the patient described, masked hypertension is defined by:</t>
+          <t>A 58-year-old man subjected to high levels of stress in the workplace, not on pharmacological treatment for arterial hypertension and with a medical history negative for significant conditions, presents to his general practitioner for a blood pressure check, reporting the finding of elevated blood pressure values (around 155/95 mmHg) during occasional measurements taken at the workplace. The physician finds levels of 138/88 mmHg (average of multiple measurements). In subjects not on antihypertensive treatment, as in the patient described, masked hypertension is defined by</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Normal blood pressure in the clinical setting and pathologically elevated outside of it (home self-measurement or 24-hour monitoring)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>Pathologically elevated blood pressure both in the clinical setting and outside of it (home self-measurement or 24-hour monitoring)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Normal blood pressure in the clinical setting and pathologically elevated outside of it (home self-measurement or 24-hour monitoring)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Grade 3 arterial hypertension</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Secondary hypertension</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Grade 3 arterial hypertension</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2473,19 +2473,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A 78-year-old minimally symptomatic patient, during self-measurement of blood pressure, detects a certain irregularity of the heartbeat. The ECG shown in the figure reveals:</t>
+          <t>A 78-year-old minimally symptomatic patient, during self-measurement of blood pressure, detects a certain irregularity of the heartbeat. The ECG shown in the figure reveals</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Sinus rhythm with second-degree atrioventricular block, Mobitz type 1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Sinus rhythm with second-degree atrioventricular block, Mobitz type 2</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Sinus rhythm with second-degree atrioventricular block, Mobitz type 1</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Sinus rhythm with blocked atrial premature beats</t>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Sinus rhythm with fascicular hemiblock of 9</t>
+          <t>Sinus rhythm with fascicular hemiblock</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Acute pulmonary embolism</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>Postoperative anemia</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Acute pulmonary embolism</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Congestive heart failure</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Deep vein thrombosis</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Congestive heart failure</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>The normal LVEF rules out the hypothesis of heart failure</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Pulmonary hilar congestion supports the diagnosis of heart failure</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>The normal LVEF rules out the hypothesis of heart failure</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Acute myopericarditis</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Acute pericarditis</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Acute myopericarditis</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>Respiratory acidosis</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>Respiratory alkalosis</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Respiratory acidosis</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>Pleural metastases from primary lung carcinoma</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>Pleural metastases from prostate carcinoma</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Pleural metastases from primary lung carcinoma</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Bronchial asthma</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Static and dynamic lung volumes within normal limits</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bronchial asthma</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Anosmia</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>Vomiting and diarrhea</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Anosmia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Between 30 and 50 days</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>More than 6 months</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Between 30 and 50 days</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Infusion of calcium gluconate 10% - 10 mL intravenously over 10 minutes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Administration of cation-exchange resin</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Infusion of calcium gluconate 10% - 10 mL intravenously over 10 minutes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The most frequent cause of chronic renal failure in Western countries is:</t>
+          <t>The most frequent cause of chronic renal failure in Western countries is</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Diabetic nephropathy</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Acute tubular necrosis</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Diabetic nephropathy</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>Psoriasis</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>Eczema</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Psoriasis</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>Methotrexate</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Hydroxychloroquine</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Methotrexate</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Subacute combined degeneration</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Amyotrophic lateral sclerosis</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Subacute combined degeneration</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>Multiple sclerosis with a lesion along the course of the left optic tract</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>Multiple sclerosis with a lesion along the course of the right optic tract</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Multiple sclerosis with a lesion along the course of the left optic tract</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>Miller Fisher syndrome</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Myasthenia gravis</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Miller Fisher syndrome</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>Specialist neuropsychiatric evaluation and electroencephalogram</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>Brain CT and electroencephalogram with sleep deprivation</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Specialist neuropsychiatric evaluation and electroencephalogram</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>Delusional mood</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>Acute paranoid delusion</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Delusional mood</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Depersonalization</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>Hallucinosis</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Depersonalization</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A 12-year-old girl has a homozygous F508del mutation in the CFTR gene and is therefore affected by cystic fibrosis. The gene responsible for the disease is located on the:</t>
+          <t>A 12-year-old girl has a homozygous F508del mutation in the CFTR gene and is therefore affected by cystic fibrosis. The gene responsible for the disease is located on the</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>Long arm of chromosome 7</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>Short arm of chromosome 13</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Long arm of chromosome 7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>Right upper limb</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>Left upper limb</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Right upper limb</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>Breath test</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>A 15-day trial with Lactobacillus reuteri</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Breath test</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>Oral food challenge</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>Prick test, applying a food extract</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Oral food challenge</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>Paracetamol 10-15 mg/kg orally</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>Paracetamol 100 mg/kg orally</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Paracetamol 10-15 mg/kg orally</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>Desmopressin</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>Betamethasone</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Desmopressin</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Hypercalcemia</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Hyperkalemia</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Hypercalcemia</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Sickle cell anemia</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>Beta-thalassemia</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Sickle cell anemia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4117,17 +4117,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Which of the following statements regarding adrenocortical carcinoma is INCORRECT:</t>
+          <t>Which of the following statements regarding adrenocortical carcinoma is INCORRECT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>Metastases spread only via the lymphatic route</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>It has an annual incidence of 0.5-2 new cases per million inhabitants</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Metastases spread only via the lymphatic route</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4175,17 +4175,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>A frequent complication of carcinoid syndrome is:</t>
+          <t>A frequent complication of carcinoid syndrome is</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>Right-sided valvular heart disease</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>Left-sided valvular heart disease</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Right-sided valvular heart disease</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>Abdominal ultrasound</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>Gastroscopy</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Abdominal ultrasound</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>All of the other answers are correct</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>Myocardial infarction</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>All of the other answers are correct</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>&gt;20 and &lt;=50 mm</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>&gt;50 mm</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>&gt;20 and &lt;=50 mm</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4407,17 +4407,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>The lymphatic vessels of the upper third of the vagina drain directly to:</t>
+          <t>The lymphatic vessels of the upper third of the vagina drain directly to</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>Iliac lymph nodes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>Superficial inguinal lymph nodes</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Iliac lymph nodes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Abdominal ultrasound</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Abdominal CT with contrast medium</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Abdominal ultrasound</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>Left gastric artery</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>Right gastric artery</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Left gastric artery</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>Pheochromocytoma</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Pancreatic endocrine tumors</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Pheochromocytoma</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>Hartmann's colonic resection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>Lavage of the peritoneal cavity and closure of the abdominal wall with multiple drains</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Hartmann's colonic resection</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>Surgery is not urgent and should be performed after improving respiratory function and correcting pulmonary hypertension</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>Surgery is urgent and must necessarily be performed within 12 hours, after correcting the respiratory distress and pulmonary hypertension</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Surgery is not urgent and should be performed after improving respiratory function and correcting pulmonary hypertension</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>The Parkland formula, also known as the Baxter formula, is used to estimate:</t>
+          <t>The Parkland formula, also known as the Baxter formula, is used to estimate</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>Fluid requirements in the burn patient</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>Caloric intake in the patient undergoing bariatric surgery</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Fluid requirements in the burn patient</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4813,17 +4813,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Rokitansky syndrome is characterized by:</t>
+          <t>Rokitansky syndrome is characterized by</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>Vaginal agenesis, absence of uterus, and presence of ovaries</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>Vaginal agenesis with presence of uterus and ovaries</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Vaginal agenesis, absence of uterus, and presence of ovaries</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>Glycoprotein</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Protein</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Glycoprotein</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>One vein, two arteries, and Wharton's jelly</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>One artery, two veins, and Wharton's jelly</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>One vein, two arteries, and Wharton's jelly</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>Uterine atony</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>Retained placental tissue</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Uterine atony</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>All of the following drugs cross the placenta, except:</t>
+          <t>All of the following drugs cross the placenta, except</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>Heparin</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Carbimazole</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Heparin</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>Amniotic fluid sampling for fetal karyotype analysis</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>Chorionic villus sampling for fetal karyotype analysis</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Amniotic fluid sampling for fetal karyotype analysis</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5224,14 +5224,14 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>Intracytoplasmic Sperm Injection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>In Vitro Fertilization and Embryo Transfer</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Intracytoplasmic Sperm Injection</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>Artificial Insemination by Husband</t>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Zygote Intra Fallopian Transfer of 19</t>
+          <t>Zygote Intra Fallopian Transfer</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5277,17 +5277,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Adhesive capsulitis of the shoulder, also known as "frozen shoulder," can frequently be associated with all of the following conditions EXCEPT ONE:</t>
+          <t>Adhesive capsulitis of the shoulder, also known as "frozen shoulder," can frequently be associated with all of the following conditions EXCEPT ONE</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>Pellegrini-Stieda syndrome</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>Neoplasms</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Pellegrini-Stieda syndrome</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>A common osteoporotic fracture is that of the femoral shaft</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>The risk of osteoporotic fracture increases after menopause</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>A common osteoporotic fracture is that of the femoral shaft</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5393,17 +5393,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>A patient must undergo hip arthroplasty surgery. After the operation, prophylaxis with low-molecular-weight heparin must be carried out:</t>
+          <t>A patient must undergo hip arthroplasty surgery. After the operation, prophylaxis with low-molecular-weight heparin must be carried out</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>For 5 weeks</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>No longer than one week because of the risk of hemorrhage</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>For 5 weeks</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>An X-ray is ordered for a 16-year-old boy following the onset over the past few weeks of severe pain and swelling of the right knee. The radiograph shows, at the level of the right distal femur, an alternation of radiolucent and radiopaque areas and a "sunburst" appearance with periosteal reaction known as Codman's triangle. The most likely diagnosis is:</t>
+          <t>An X-ray is ordered for a 16-year-old boy following the onset over the past few weeks of severe pain and swelling of the right knee. The radiograph shows, at the level of the right distal femur, an alternation of radiolucent and radiopaque areas and a "sunburst" appearance with periosteal reaction known as Codman's triangle. The most likely diagnosis is</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>Osteosarcoma</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>Osteoclastoma</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Osteosarcoma</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>Subcapital fracture of the left femur</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>Transcervical fracture of the left femur</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Subcapital fracture of the left femur</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>Emergency surgical intervention within 6 hours</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>Analgesics until complete resolution of the pain</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Emergency surgical intervention within 6 hours</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>Acute right orchiepididymitis</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>Testicular torsion</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Acute right orchiepididymitis</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5693,17 +5693,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Hematuria can be caused by:</t>
+          <t>Hematuria can be caused by</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>All the other answers are correct</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>Cystitis</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>All the other answers are correct</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>Apply the ABCDE protocol (Airway, Breathing, Circulation, Disability, Exposure) according to ATLS (Advanced Trauma Life Support) guidelines</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>Contrast-enhanced brain CT</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Apply the ABCDE protocol (Airway, Breathing, Circulation, Disability, Exposure) according to ATLS (Advanced Trauma Life Support) guidelines</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>Chronic subdural hematoma</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>Acute subdural hematoma</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Chronic subdural hematoma</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>Cataract</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>Hypertensive retinopathy</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Cataract</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5935,17 +5935,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>A 45-year-old man, hyperopic by 6 diopters, presents to the Emergency Department complaining of severe pain and blurred vision in the right eye, which also appears markedly hyperemic. On slit-lamp examination, in addition to conjunctival and perikeratic hyperemia, there is corneal edema, a mid-dilated pupil unreactive to light stimuli, and an extremely shallow anterior chamber; the eye is hard on palpation. It can therefore be concluded that the patient has:</t>
+          <t>A 45-year-old man, hyperopic by 6 diopters, presents to the Emergency Department complaining of severe pain and blurred vision in the right eye, which also appears markedly hyperemic. On slit-lamp examination, in addition to conjunctival and perikeratic hyperemia, there is corneal edema, a mid-dilated pupil unreactive to light stimuli, and an extremely shallow anterior chamber; the eye is hard on palpation. It can therefore be concluded that the patient has</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>An acute attack of glaucoma</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>Viral keratoconjunctivitis</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>An acute attack of glaucoma</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>A 40-year-old man undergoes an ophthalmologic examination because he wants to change his glasses. During the examination, a pronounced cupping of the optic nerve and a nasal displacement of the emergence of the retinal vascular tree from the optic disc are noted in both eyes. The intraocular pressure is 15 mmHg. A Visual Field test is then requested, which reveals a localized "arcuate scotoma"-type defect bilaterally. The patient reports having no significant medical conditions and, in fact, tends to be hypotensive, generally having a blood pressure of 105/65 mmHg. The most likely diagnosis is:</t>
+          <t>A 40-year-old man undergoes an ophthalmologic examination because he wants to change his glasses. During the examination, a pronounced cupping of the optic nerve and a nasal displacement of the emergence of the retinal vascular tree from the optic disc are noted in both eyes. The intraocular pressure is 15 mmHg. A Visual Field test is then requested, which reveals a localized "arcuate scotoma"-type defect bilaterally. The patient reports having no significant medical conditions and, in fact, tends to be hypotensive, generally having a blood pressure of 105/65 mmHg. The most likely diagnosis is</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>Low-tension glaucoma</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>Ischemic optic neuropathy</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Low-tension glaucoma</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>Endoscopic surgery</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>Radiotherapy</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Endoscopic surgery</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>Treacher-Collins syndrome</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>Whipple syndrome</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Treacher-Collins syndrome</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>MRI with gadolinium</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>CT without contrast medium</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>MRI with gadolinium</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>Ostium secundum type ASD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>Ostium primum type ASD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Ostium secundum type ASD</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>Segmentectomy/wedge resection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>Pneumonectomy</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Segmentectomy/wedge resection</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>Control of cardiovascular risk factors, optimization of medical therapy, walking training, and clinical follow-up</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>Hospital admission to perform surgical placement of a right femoropopliteal bypass</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Control of cardiovascular risk factors, optimization of medical therapy, walking training, and clinical follow-up</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>Use of an antiplatelet agent</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>Use of low-molecular-weight heparin</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Use of an antiplatelet agent</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>Leydig cell tumor</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>Embryonal carcinoma</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Leydig cell tumor</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
+          <t>Pilocytic astrocytoma</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t>Optic nerve glioma and mesothelioma</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Pilocytic astrocytoma</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t>In approximately 60% of cases it originates in T-NK cells and only in 40% is it of B-cell origin</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>Bone marrow involvement is frequent</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>In approximately 60% of cases it originates in T-NK cells and only in 40% is it of B-cell origin</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wilms tumor is a neoplasm of the:</t>
+          <t>Wilms tumor is a neoplasm of the</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>Kidney</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>Lung</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Kidney</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>Chlamydia trachomatis</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t>Gardnerella vaginalis</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Chlamydia trachomatis</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>Staphylococcus aureus</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>A 25-year-old patient diagnosed with Gilbert syndrome shows the following on periodic blood tests:</t>
+          <t>A 25-year-old patient diagnosed with Gilbert syndrome shows the following on periodic blood tests</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>Fluctuating hyperbilirubinemia</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>Persistent hyperbilirubinemia</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Fluctuating hyperbilirubinemia</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>Hypoparathyroidism</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>Biliary tract obstruction</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Hypoparathyroidism</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6926,14 +6926,14 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
+          <t>CT of the entire abdomen without contrast medium</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t>CT of the entire abdomen with contrast medium</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>CT of the entire abdomen without contrast medium</t>
-        </is>
-      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t>Plain abdominal radiograph</t>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Contrast-enhanced ultrasound of the 26</t>
+          <t>Contrast-enhanced ultrasound of the</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6984,22 +6984,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>T2 sequence with contrast medium of the 27</t>
+          <t>Image A: T1 sequence; Image B: T2 sequence</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>T2 sequence; Image</t>
+          <t>Image A: T2 sequence; Image B: T1 sequence</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Image A: T1-weighted sequence; Image B: T1-weighted sequence with contrast</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Image A: T2 sequence; Image B: T1 sequence with contrast medium</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
+          <t>Left pneumothorax</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>Right pneumothorax</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Left pneumothorax</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
+          <t>Brain MRI without and with contrast, with evaluation of the sella turcica</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>Brain MRI without contrast, with evaluation of the sella turcica</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Brain MRI without and with contrast, with evaluation of the sella turcica</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7178,14 +7178,14 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
+          <t>Presence of a subdiaphragmatic crescent of air</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t>Presence of a supradiaphragmatic crescent of air</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Presence of a subdiaphragmatic crescent of air</t>
-        </is>
-      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>Presence of epigastric opacity</t>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Elevation of the left hemidiaphragm by 28</t>
+          <t>Elevation of the left hemidiaphragm by</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7236,12 +7236,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
+          <t>Infarction of the distal portion of the spinal cord resulting from acute ischemia in the territory of the anterior spinal artery (anterior spinal artery syndrome)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t>Brown-Séquard syndrome</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Infarction of the distal portion of the spinal cord resulting from acute ischemia in the territory of the anterior spinal artery (anterior spinal artery syndrome)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>In the event that complete surgical excision cannot be performed, external beam radiotherapy may be considered for palliative purposes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t>These are radiosensitive tumors, so the use of radiotherapy is generally considered in the treatment planning</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>In the event that complete surgical excision cannot be performed, external beam radiotherapy may be considered for palliative purposes</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7347,17 +7347,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>A 55-year-old woman with an unremarkable medical history and an active lifestyle is admitted to the intensive care unit for a urinary tract infection. The patient remains hypotensive despite infusion of 2,000 mL of fluids (blood pressure 75/50 mmHg). Blood gas analysis shows lactate of 4.7 mmol/L. This condition can be defined as:</t>
+          <t>A 55-year-old woman with an unremarkable medical history and an active lifestyle is admitted to the intensive care unit for a urinary tract infection. The patient remains hypotensive despite infusion of 2,000 mL of fluids (blood pressure 75/50 mmHg). Blood gas analysis shows lactate of 4.7 mmol/L. This condition can be defined as</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
+          <t>Septic shock</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>Sepsis</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Septic shock</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
+          <t>Fluid loading in suspected renal failure, including possible prerenal failure</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>Low-dose norepinephrine</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Fluid loading in suspected renal failure, including possible prerenal failure</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>Metabolic alkalosis</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>Metabolic acidosis</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Metabolic alkalosis</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
+          <t>Chronic obstructive pulmonary disease with FEV1 &gt;70% predicted</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t>Massive pneumonia</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Chronic obstructive pulmonary disease with FEV1 &gt;70% predicted</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7642,14 +7642,14 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
+          <t>Norepinephrine</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>Epinephrine</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Norepinephrine</t>
-        </is>
-      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t>Propranolol</t>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Isoprenaline 30</t>
+          <t>Isoprenaline</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>Rapid administration of colloids</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t>Obtain cultures before administering antibiotics</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Rapid administration of colloids</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7753,17 +7753,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>The subject of Law 38 of March 2010 is:</t>
+          <t>The subject of Law 38 of March 2010 is</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
+          <t>Provisions to ensure access to palliative care and pain therapy</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t>Provisions concerning informed consent and advance treatment directives</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Provisions to ensure access to palliative care and pain therapy</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
+          <t>Non-weight-bearing ambulation for at least 4-5 weeks and assisted knee kinesiotherapy</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t>Full weight-bearing from postoperative day 1</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Non-weight-bearing ambulation for at least 4-5 weeks and assisted knee kinesiotherapy</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>At least 8 weeks, with variable extension up to 12 weeks</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>Pulmonary rehabilitation is not part of the treatment of COPD</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>At least 8 weeks, with variable extension up to 12 weeks</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A healthy 40-year-old woman has a mutation of the BRCA1 gene, which is also present in her sister, who has breast cancer. Her mother died at the age of 72 from a cerebral stroke. This situation indicates that:</t>
+          <t>A healthy 40-year-old woman has a mutation of the BRCA1 gene, which is also present in her sister, who has breast cancer. Her mother died at the age of 72 from a cerebral stroke. This situation indicates that</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
+          <t>The woman will develop breast cancer</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t>50% of the woman's daughters will develop breast cancer</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>The woman will develop breast cancer</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7985,17 +7985,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Which of these drugs most frequently causes thyroid dysfunction:</t>
+          <t>Which of these drugs most frequently causes thyroid dysfunction</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
+          <t>Amiodarone</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t>Beta-blockers</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Amiodarone</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
+          <t>Constipation, nausea, and vomiting</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t>Diarrhea and headache</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Constipation, nausea, and vomiting</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
+          <t>ACE inhibitors</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>Calcium channel blockers</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>ACE inhibitors</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Indicate which of the following statements about mass screening programs is FALSE:</t>
+          <t>Indicate which of the following statements about mass screening programs is FALSE</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
+          <t>The result of the screening test has diagnostic value</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t>They are systematic and organized preventive interventions</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>The result of the screening test has diagnostic value</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8217,17 +8217,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Gaia's mother, alarmed by media misinformation regarding the vaccine issue and by the adverse reactions that occurred in her two-year-old nephew, turns to the family pediatrician to ask for information and advice. The pediatrician reassures her about the safety and efficacy of all vaccines and specifies that:</t>
+          <t>Gaia's mother, alarmed by media misinformation regarding the vaccine issue and by the adverse reactions that occurred in her two-year-old nephew, turns to the family pediatrician to ask for information and advice. The pediatrician reassures her about the safety and efficacy of all vaccines and specifies that</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
+          <t>Pneumococcal vaccination is recommended</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>Rotavirus vaccination has become mandatory</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Pneumococcal vaccination is recommended</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>Only if the subject has received 3 or more doses of vaccine within the last 5 years</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>Only if the wound is neither severe nor deep, regardless of the subject's vaccination status</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Only if the subject has received 3 or more doses of vaccine within the last 5 years</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
+          <t>Invasive listeriosis</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
           <t>Campylobacteriosis</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Invasive listeriosis</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>Arterial hypertension</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t>Arterial hypotension</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Arterial hypertension</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
+          <t>Neutropenia</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
           <t>Presence of specific IgG precipitating antibodies ("precipitins")</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Neutropenia</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8507,19 +8507,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>In Italy, in the exercise of their profession, a physician may invoke conscientious objection in the following cases. All of the answers are correct EXCEPT ONE:</t>
+          <t>In Italy, in the exercise of their profession, a physician may invoke conscientious objection in the following cases. All of the answers are correct EXCEPT ONE</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
+          <t>Regarding organ procurement for transplantation purposes (Law 519/1968)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t>Regarding voluntary termination of pregnancy after the first 90 days from conception (Law 194/1978)</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Regarding organ procurement for transplantation purposes (Law 519/1968)</t>
-        </is>
-      </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>Regarding animal experimentation (Law 413/1993)</t>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Regarding voluntary termination of pregnancy within the first 90 days from conception (Law 194/1978) of 33</t>
+          <t>Regarding voluntary termination of pregnancy within the first 90 days from conception (Law 194/1978)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8565,17 +8565,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>A grandmother comes to the Emergency Department with her 10-month-old granddaughter. The grandmother reports an unwitnessed fall from a high chair, as she was in another room at the time. The child presents with multiple bruises on the upper and lower limbs at different stages of color change, and minor abrasions on the left arm and left leg. During the examination, the pediatrician notes a marked painful response to mobilization of the lower limbs and therefore a targeted X-ray is decided upon, which diagnoses a metaphyseal fracture of the right femur in a non-ambulatory pediatric patient, suggesting that the trauma was not accidental. The physician must decide whether or not to report the matter to the judicial authority, because:</t>
+          <t>A grandmother comes to the Emergency Department with her 10-month-old granddaughter. The grandmother reports an unwitnessed fall from a high chair, as she was in another room at the time. The child presents with multiple bruises on the upper and lower limbs at different stages of color change, and minor abrasions on the left arm and left leg. During the examination, the pediatrician notes a marked painful response to mobilization of the lower limbs and therefore a targeted X-ray is decided upon, which diagnoses a metaphyseal fracture of the right femur in a non-ambulatory pediatric patient, suggesting that the trauma was not accidental. The physician must decide whether or not to report the matter to the judicial authority, because</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
+          <t>A report/complaint addressed to the public prosecutor is mandatory</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t>The report/complaint may be omitted because it would expose the person concerned to criminal proceedings</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>A report/complaint addressed to the public prosecutor is mandatory</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
+          <t>It is asymmetric with respect to the mean value</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
           <t>It is asymptotic to the x-axis on both sides</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>It is asymmetric with respect to the mean value</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2020_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2020_EN.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Cardiology and Cardiac Surgery</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Hematology; Pharmacology and Toxicology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Hematology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Urology; Pharmacology and Toxicology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Oncology; Orthopedics and Traumatology</t>
+          <t>Hematology; Pediatrics</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; Infectious Diseases</t>
+          <t>Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Hematology; Oncology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Cardiology and Cardiac Surgery</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Immunology and Rheumatology; Pharmacology and Toxicology</t>
+          <t>Immunology and Rheumatology</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Hematology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Ophthalmology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Pediatrics; Oncology</t>
+          <t>Pediatrics; Hematology</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Hematology; Pediatrics</t>
+          <t>Pediatrics; Hematology</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>General Surgery; Anesthesia and Intensive Care</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Endocrinology</t>
+          <t>Endocrinology; Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pharmacology and Toxicology</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Medical Genetics; Otorhinolaryngology</t>
+          <t>Medical Genetics</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Otorhinolaryngology; Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Neurology and Neurosurgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Infectious Diseases</t>
+          <t>Infectious Diseases; Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Urology</t>
+          <t>Urology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Nephrology; Pharmacology and Toxicology</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Nephrology</t>
+          <t>Nephrology; Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Infectious Diseases</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2020_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2020_EN.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/EN/xlsx/ITAMed_2020_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2020_EN.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -473,15 +473,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Image Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Image Path</t>
         </is>
@@ -541,7 +546,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,6 +612,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -660,6 +675,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -718,6 +738,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,6 +801,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -834,6 +864,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +927,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -950,6 +990,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1008,6 +1053,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1063,7 +1113,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1124,6 +1179,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1182,6 +1242,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1240,6 +1305,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1298,6 +1368,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1356,6 +1431,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1414,6 +1494,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1472,6 +1557,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1530,6 +1620,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1588,6 +1683,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1646,6 +1746,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1704,6 +1809,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1762,6 +1872,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1820,6 +1935,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1878,6 +1998,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1936,6 +2061,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1994,6 +2124,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2052,6 +2187,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2110,6 +2250,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2168,6 +2313,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2226,6 +2376,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2284,6 +2439,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2342,6 +2502,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2400,6 +2565,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2458,6 +2628,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2518,10 +2693,15 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>images/2020/ssm20203813554.png</t>
         </is>
@@ -2586,10 +2766,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>images/2020/ssm20203813604.png</t>
         </is>
@@ -2652,6 +2837,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2710,6 +2900,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2768,6 +2963,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2826,6 +3026,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2884,6 +3089,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2942,6 +3152,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3000,6 +3215,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3058,6 +3278,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3116,6 +3341,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3174,6 +3404,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3232,6 +3467,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3290,6 +3530,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3348,6 +3593,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3406,6 +3656,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3464,6 +3719,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3522,6 +3782,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3580,6 +3845,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3638,6 +3908,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3696,6 +3971,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3754,6 +4034,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3812,6 +4097,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3870,6 +4160,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3928,6 +4223,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3986,6 +4286,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4044,6 +4349,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4102,6 +4412,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4160,6 +4475,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4218,6 +4538,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4276,6 +4601,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4334,6 +4664,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4392,6 +4727,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4450,6 +4790,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4508,6 +4853,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4566,6 +4916,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4624,6 +4979,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4682,6 +5042,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4740,6 +5105,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4798,6 +5168,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4856,6 +5231,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4914,6 +5294,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4972,6 +5357,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5030,6 +5420,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5088,6 +5483,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5146,6 +5546,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5204,6 +5609,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5262,6 +5672,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5320,6 +5735,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5378,6 +5798,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5436,6 +5861,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5494,6 +5924,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5554,10 +5989,15 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
           <t>Pelvic X-ray</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>images/2020/ssm20203816154.png</t>
         </is>
@@ -5620,6 +6060,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5678,6 +6123,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5736,6 +6186,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5794,6 +6249,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5854,10 +6314,15 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
           <t>Brain MRI</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>images/2020/ssm20203816404.png</t>
         </is>
@@ -5920,6 +6385,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5978,6 +6448,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6036,6 +6511,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6094,6 +6574,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6152,6 +6637,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6210,6 +6700,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6268,6 +6763,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6326,6 +6826,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6384,6 +6889,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6442,6 +6952,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6500,6 +7015,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6558,6 +7078,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6616,6 +7141,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6674,6 +7204,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6732,6 +7267,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6787,7 +7327,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6848,6 +7393,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6906,6 +7456,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6964,6 +7519,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7024,10 +7584,15 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
           <t>Brain MRI</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr">
+      <c r="O113" t="inlineStr">
         <is>
           <t>images/2020/ssm20203817404.png</t>
         </is>
@@ -7092,10 +7657,15 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
           <t>Chest CT scan</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t>images/2020/ssm20203817454.png</t>
         </is>
@@ -7158,6 +7728,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7216,6 +7791,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7274,6 +7854,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7332,6 +7917,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7390,6 +7980,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7448,6 +8043,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7506,6 +8106,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7564,6 +8169,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7622,6 +8232,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7680,6 +8295,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7738,6 +8358,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7796,6 +8421,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7854,6 +8484,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7912,6 +8547,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7970,6 +8610,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8028,6 +8673,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8086,6 +8736,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8144,6 +8799,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8202,6 +8862,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8260,6 +8925,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8318,6 +8988,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8376,6 +9051,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8434,6 +9114,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8492,6 +9177,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8550,6 +9240,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8608,6 +9303,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8664,6 +9364,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
